--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T14:37:20+00:00</t>
+    <t>2026-09-07T15:18:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:18:54+00:00</t>
+    <t>2026-09-07T18:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:27:01+00:00</t>
+    <t>2026-09-07T18:38:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:38:14+00:00</t>
+    <t>2026-09-08T08:42:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:42:22+00:00</t>
+    <t>2026-09-08T08:49:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T08:49:15+00:00</t>
+    <t>2026-09-08T09:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:59:59+00:00</t>
+    <t>2026-09-08T14:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:28:13+00:00</t>
+    <t>2026-09-08T14:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:35:38+00:00</t>
+    <t>2026-09-08T14:50:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T14:50:12+00:00</t>
+    <t>2026-09-08T15:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:07:59+00:00</t>
+    <t>2026-09-08T15:32:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:32:50+00:00</t>
+    <t>2026-09-08T17:49:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T17:49:28+00:00</t>
+    <t>2026-09-08T19:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T19:41:07+00:00</t>
+    <t>2026-09-12T21:08:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T21:08:11+00:00</t>
+    <t>2026-09-12T22:28:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc2/StructureDefinition-mii-lm-dokument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T22:28:47+00:00</t>
+    <t>2026-09-12T22:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
